--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0007_ses-01_pet_pdf.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0007_ses-01_pet_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -243,7 +244,7 @@
         <v>0.018590816136828409</v>
       </c>
       <c r="V1" s="0">
-        <v>0.19914215686274508</v>
+        <v>0.19914215686274509</v>
       </c>
       <c r="W1" s="0">
         <v>0.017094017094017096</v>
@@ -390,7 +391,7 @@
         <v>0.096875756841850333</v>
       </c>
       <c r="BS1" s="0">
-        <v>0.0080778706732905214</v>
+        <v>0.0080778706732905215</v>
       </c>
       <c r="BT1" s="0">
         <v>0</v>
@@ -605,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="0">
-        <v>0.030637254901960786</v>
+        <v>0.030637254901960787</v>
       </c>
       <c r="W2" s="0">
         <v>0</v>
@@ -752,7 +753,7 @@
         <v>0.040364898684104304</v>
       </c>
       <c r="BS2" s="0">
-        <v>0.0080778706732905214</v>
+        <v>0.0080778706732905215</v>
       </c>
       <c r="BT2" s="0">
         <v>0</v>
@@ -1174,7 +1175,7 @@
         <v>0.0031577617784514338</v>
       </c>
       <c r="CM3" s="0">
-        <v>0.13042668157257314</v>
+        <v>0.13042668157257315</v>
       </c>
       <c r="CN3" s="0">
         <v>0</v>
@@ -1329,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="0">
-        <v>0.030637254901960786</v>
+        <v>0.030637254901960787</v>
       </c>
       <c r="W4" s="0">
         <v>0</v>
@@ -1416,7 +1417,7 @@
         <v>0.030385900941962928</v>
       </c>
       <c r="AY4" s="0">
-        <v>0.020222446916076844</v>
+        <v>0.020222446916076845</v>
       </c>
       <c r="AZ4" s="0">
         <v>0</v>
@@ -1545,7 +1546,7 @@
         <v>0.079344088865379525</v>
       </c>
       <c r="CP4" s="0">
-        <v>0.0039972818483431267</v>
+        <v>0.0039972818483431268</v>
       </c>
       <c r="CQ4" s="0">
         <v>0</v>
@@ -1724,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="AG5" s="0">
-        <v>0.037724460540214277</v>
+        <v>0.037724460540214278</v>
       </c>
       <c r="AH5" s="0">
         <v>0.14272121788772599</v>
@@ -1838,7 +1839,7 @@
         <v>0.040364898684104304</v>
       </c>
       <c r="BS5" s="0">
-        <v>0.0080778706732905214</v>
+        <v>0.0080778706732905215</v>
       </c>
       <c r="BT5" s="0">
         <v>0</v>
@@ -1907,7 +1908,7 @@
         <v>0.074936083928413999</v>
       </c>
       <c r="CP5" s="0">
-        <v>0.02398369109005876</v>
+        <v>0.023983691090058761</v>
       </c>
       <c r="CQ5" s="0">
         <v>0</v>
@@ -2529,7 +2530,7 @@
         <v>0.086260012322858903</v>
       </c>
       <c r="BH7" s="0">
-        <v>0.022311468094600623</v>
+        <v>0.022311468094600624</v>
       </c>
       <c r="BI7" s="0">
         <v>0.096826250672404524</v>
@@ -2562,7 +2563,7 @@
         <v>0.12109469605231292</v>
       </c>
       <c r="BS7" s="0">
-        <v>0.0080778706732905214</v>
+        <v>0.0080778706732905215</v>
       </c>
       <c r="BT7" s="0">
         <v>0.0042398032731281272</v>
@@ -2583,7 +2584,7 @@
         <v>0.083612040133779264</v>
       </c>
       <c r="BZ7" s="0">
-        <v>0.14481305950500264</v>
+        <v>0.14481305950500265</v>
       </c>
       <c r="CA7" s="0">
         <v>0</v>
@@ -2777,7 +2778,7 @@
         <v>0.018590816136828409</v>
       </c>
       <c r="V8" s="0">
-        <v>0.19914215686274508</v>
+        <v>0.19914215686274509</v>
       </c>
       <c r="W8" s="0">
         <v>0.017094017094017096</v>
@@ -2978,7 +2979,7 @@
         <v>0.021083702298123553</v>
       </c>
       <c r="CK8" s="0">
-        <v>0.16744714062721724</v>
+        <v>0.16744714062721725</v>
       </c>
       <c r="CL8" s="0">
         <v>0.04736642667677151</v>
@@ -3244,7 +3245,7 @@
         <v>0.17814319972593337</v>
       </c>
       <c r="BE9" s="0">
-        <v>0.031254883575558653</v>
+        <v>0.031254883575558654</v>
       </c>
       <c r="BF9" s="0">
         <v>0</v>
@@ -3298,7 +3299,7 @@
         <v>0.065520065520065465</v>
       </c>
       <c r="BW9" s="0">
-        <v>0.04385964912280698</v>
+        <v>0.043859649122806981</v>
       </c>
       <c r="BX9" s="0">
         <v>0.07011639321273308</v>
@@ -3334,7 +3335,7 @@
         <v>0.013250298131707952</v>
       </c>
       <c r="CI9" s="0">
-        <v>0.044370493621741502</v>
+        <v>0.044370493621741503</v>
       </c>
       <c r="CJ9" s="0">
         <v>0.042167404596247064</v>
@@ -3510,7 +3511,7 @@
         <v>0.075800644305476672</v>
       </c>
       <c r="Y10" s="0">
-        <v>0.078616352201257927</v>
+        <v>0.078616352201257928</v>
       </c>
       <c r="Z10" s="0">
         <v>0.5719514985129267</v>
@@ -3528,7 +3529,7 @@
         <v>0.047585058291696451</v>
       </c>
       <c r="AE10" s="0">
-        <v>0.068306010928961824</v>
+        <v>0.068306010928961825</v>
       </c>
       <c r="AF10" s="0">
         <v>0</v>
@@ -3702,7 +3703,7 @@
         <v>0.052709255745308922</v>
       </c>
       <c r="CK10" s="0">
-        <v>0.21285653469561538</v>
+        <v>0.21285653469561539</v>
       </c>
       <c r="CL10" s="0">
         <v>0.094732853353543103</v>
@@ -3863,7 +3864,7 @@
         <v>0.037181632273656784</v>
       </c>
       <c r="V11" s="0">
-        <v>0.29105392156862719</v>
+        <v>0.2910539215686272</v>
       </c>
       <c r="W11" s="0">
         <v>0.034188034188034157</v>
@@ -4037,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="CB11" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC11" s="0">
         <v>0.099987501562304626</v>
@@ -4228,7 +4229,7 @@
         <v>0.30637254901960814</v>
       </c>
       <c r="W12" s="0">
-        <v>0.068376068376068438</v>
+        <v>0.068376068376068439</v>
       </c>
       <c r="X12" s="0">
         <v>0.18950161076369168</v>
@@ -4288,7 +4289,7 @@
         <v>0.14716703458425326</v>
       </c>
       <c r="AQ12" s="0">
-        <v>0.5007153075822609</v>
+        <v>0.50071530758226091</v>
       </c>
       <c r="AR12" s="0">
         <v>0</v>
@@ -4354,7 +4355,7 @@
         <v>0.1018978474079736</v>
       </c>
       <c r="BM12" s="0">
-        <v>0.046352627614577951</v>
+        <v>0.046352627614577952</v>
       </c>
       <c r="BN12" s="0">
         <v>0.051743764876332456</v>
@@ -4560,7 +4561,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="0">
-        <v>0.027720027720027698</v>
+        <v>0.027720027720027699</v>
       </c>
       <c r="N13" s="0">
         <v>0.010384215991692619</v>
@@ -4611,7 +4612,7 @@
         <v>0.070921985815602773</v>
       </c>
       <c r="AD13" s="0">
-        <v>0.071377587437544548</v>
+        <v>0.071377587437544549</v>
       </c>
       <c r="AE13" s="0">
         <v>0</v>
@@ -4668,7 +4669,7 @@
         <v>0.20120724346076441</v>
       </c>
       <c r="AW13" s="0">
-        <v>0.50233225690706806</v>
+        <v>0.50233225690706807</v>
       </c>
       <c r="AX13" s="0">
         <v>0.11141497012053064</v>
@@ -4764,7 +4765,7 @@
         <v>0.2099737532808397</v>
       </c>
       <c r="CC13" s="0">
-        <v>0.074990626171728469</v>
+        <v>0.07499062617172847</v>
       </c>
       <c r="CD13" s="0">
         <v>0.34615384615384587</v>
@@ -4910,7 +4911,7 @@
         <v>0.010091835704914733</v>
       </c>
       <c r="I14" s="0">
-        <v>0.044296788482835039</v>
+        <v>0.04429678848283504</v>
       </c>
       <c r="J14" s="0">
         <v>0.019182812200268577</v>
@@ -4943,7 +4944,7 @@
         <v>0.01857527630723509</v>
       </c>
       <c r="T14" s="0">
-        <v>0.034146008331626065</v>
+        <v>0.034146008331626066</v>
       </c>
       <c r="U14" s="0">
         <v>0.18590816136828425</v>
@@ -4952,7 +4953,7 @@
         <v>0.5514705882352946</v>
       </c>
       <c r="W14" s="0">
-        <v>0.068376068376068438</v>
+        <v>0.068376068376068439</v>
       </c>
       <c r="X14" s="0">
         <v>0.09475080538184584</v>
@@ -4976,7 +4977,7 @@
         <v>0.23792529145848226</v>
       </c>
       <c r="AE14" s="0">
-        <v>0.068306010928961824</v>
+        <v>0.068306010928961825</v>
       </c>
       <c r="AF14" s="0">
         <v>0</v>
@@ -4991,7 +4992,7 @@
         <v>0.33444816053511739</v>
       </c>
       <c r="AJ14" s="0">
-        <v>0.45407636738906137</v>
+        <v>0.45407636738906138</v>
       </c>
       <c r="AK14" s="0">
         <v>0.014857737166629538</v>
@@ -5024,7 +5025,7 @@
         <v>0.055648302726766886</v>
       </c>
       <c r="AU14" s="0">
-        <v>0.51928783382789367</v>
+        <v>0.51928783382789368</v>
       </c>
       <c r="AV14" s="0">
         <v>0.19375512333258832</v>
@@ -5093,7 +5094,7 @@
         <v>0.39483129935391281</v>
       </c>
       <c r="BR14" s="0">
-        <v>0.40364898684104344</v>
+        <v>0.40364898684104345</v>
       </c>
       <c r="BS14" s="0">
         <v>0.13732380144593898</v>
@@ -5156,7 +5157,7 @@
         <v>0.21157003915624625</v>
       </c>
       <c r="CM14" s="0">
-        <v>0.59623625861747775</v>
+        <v>0.59623625861747776</v>
       </c>
       <c r="CN14" s="0">
         <v>0.10768126346015804</v>
@@ -5257,7 +5258,7 @@
         <v>0.020621593754603016</v>
       </c>
       <c r="D15" s="0">
-        <v>0.024588148512416991</v>
+        <v>0.024588148512416992</v>
       </c>
       <c r="E15" s="0">
         <v>0.018689842070834486</v>
@@ -5275,7 +5276,7 @@
         <v>0.044296788482834956</v>
       </c>
       <c r="J15" s="0">
-        <v>0.044759895133959927</v>
+        <v>0.044759895133959928</v>
       </c>
       <c r="K15" s="0">
         <v>0.038008361839604682</v>
@@ -5359,7 +5360,7 @@
         <v>0.01485773716662951</v>
       </c>
       <c r="AL15" s="0">
-        <v>0.051589604694653977</v>
+        <v>0.051589604694653978</v>
       </c>
       <c r="AM15" s="0">
         <v>0.43249922767995014</v>
@@ -5452,7 +5453,7 @@
         <v>0.014697236919459128</v>
       </c>
       <c r="BQ15" s="0">
-        <v>0.35893754486719281</v>
+        <v>0.35893754486719282</v>
       </c>
       <c r="BR15" s="0">
         <v>0.40364898684104267</v>
@@ -5622,7 +5623,7 @@
         <v>0.057372346528973092</v>
       </c>
       <c r="E16" s="0">
-        <v>0.01868984207083452</v>
+        <v>0.018689842070834521</v>
       </c>
       <c r="F16" s="0">
         <v>0.040171013744225458</v>
@@ -5772,7 +5773,7 @@
         <v>0.029568302779420491</v>
       </c>
       <c r="BC16" s="0">
-        <v>0.093109869646182591</v>
+        <v>0.093109869646182592</v>
       </c>
       <c r="BD16" s="0">
         <v>0.57553956834532427</v>
@@ -5814,10 +5815,10 @@
         <v>0.029394473838918311</v>
       </c>
       <c r="BQ16" s="0">
-        <v>0.32304379038047409</v>
+        <v>0.3230437903804741</v>
       </c>
       <c r="BR16" s="0">
-        <v>0.4763058044724312</v>
+        <v>0.47630580447243121</v>
       </c>
       <c r="BS16" s="0">
         <v>0.19386889615897268</v>
@@ -5993,7 +5994,7 @@
         <v>0.080128205128205066</v>
       </c>
       <c r="H17" s="0">
-        <v>0.050459178524573572</v>
+        <v>0.050459178524573573</v>
       </c>
       <c r="I17" s="0">
         <v>0.094130675526024277</v>
@@ -6008,7 +6009,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="0">
-        <v>0.027720027720027698</v>
+        <v>0.027720027720027699</v>
       </c>
       <c r="N17" s="0">
         <v>0.051921079958463089</v>
@@ -6038,7 +6039,7 @@
         <v>0.62806372549019551</v>
       </c>
       <c r="W17" s="0">
-        <v>0.20512820512820495</v>
+        <v>0.20512820512820496</v>
       </c>
       <c r="X17" s="0">
         <v>0.17055144968732219</v>
@@ -6523,7 +6524,7 @@
         <v>0.54261968541795402</v>
       </c>
       <c r="BL18" s="0">
-        <v>0.48401477518787372</v>
+        <v>0.48401477518787373</v>
       </c>
       <c r="BM18" s="0">
         <v>0.34764470710933393</v>
@@ -6822,7 +6823,7 @@
         <v>0.33848417954378318</v>
       </c>
       <c r="AQ19" s="0">
-        <v>0.94420600858369363</v>
+        <v>0.94420600858369364</v>
       </c>
       <c r="AR19" s="0">
         <v>0.074766355140187132</v>
@@ -6915,7 +6916,7 @@
         <v>0.25904051393638039</v>
       </c>
       <c r="BV19" s="0">
-        <v>0.2620802620802628</v>
+        <v>0.26208026208026281</v>
       </c>
       <c r="BW19" s="0">
         <v>0.29239766081871427</v>
@@ -7079,7 +7080,7 @@
         <v>0.093482905982905901</v>
       </c>
       <c r="H20" s="0">
-        <v>0.050459178524573572</v>
+        <v>0.050459178524573573</v>
       </c>
       <c r="I20" s="0">
         <v>0.10520487264673302</v>
@@ -7205,7 +7206,7 @@
         <v>1.1481880157875841</v>
       </c>
       <c r="AX20" s="0">
-        <v>0.41527397954015965</v>
+        <v>0.41527397954015966</v>
       </c>
       <c r="AY20" s="0">
         <v>0.55274688237276659</v>
@@ -7235,7 +7236,7 @@
         <v>0.78250154035736219</v>
       </c>
       <c r="BH20" s="0">
-        <v>0.32909415439535888</v>
+        <v>0.32909415439535889</v>
       </c>
       <c r="BI20" s="0">
         <v>0.75667921821767903</v>
@@ -7319,7 +7320,7 @@
         <v>0.54353854686633341</v>
       </c>
       <c r="CJ20" s="0">
-        <v>0.37950664136622358</v>
+        <v>0.37950664136622359</v>
       </c>
       <c r="CK20" s="0">
         <v>0.85142613878245987</v>
@@ -7441,7 +7442,7 @@
         <v>0.17361111111111094</v>
       </c>
       <c r="H21" s="0">
-        <v>0.050459178524573572</v>
+        <v>0.050459178524573573</v>
       </c>
       <c r="I21" s="0">
         <v>0.13842746400885925</v>
@@ -7462,7 +7463,7 @@
         <v>0.07268951194184832</v>
       </c>
       <c r="O21" s="0">
-        <v>0.098872849515522956</v>
+        <v>0.098872849515522957</v>
       </c>
       <c r="P21" s="0">
         <v>0.05118580447022688</v>
@@ -7654,7 +7655,7 @@
         <v>0.85571353343865109</v>
       </c>
       <c r="CA21" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB21" s="0">
         <v>0.47244094488188931</v>
@@ -7672,7 +7673,7 @@
         <v>0.57570523891767367</v>
       </c>
       <c r="CG21" s="0">
-        <v>0.55545707025940982</v>
+        <v>0.55545707025940983</v>
       </c>
       <c r="CH21" s="0">
         <v>0.17225387571220338</v>
@@ -7684,7 +7685,7 @@
         <v>0.43221589711153241</v>
       </c>
       <c r="CK21" s="0">
-        <v>0.91386405562650685</v>
+        <v>0.91386405562650686</v>
       </c>
       <c r="CL21" s="0">
         <v>0.63786787924718902</v>
@@ -7693,7 +7694,7 @@
         <v>1.043413452580584</v>
       </c>
       <c r="CN21" s="0">
-        <v>0.35893754486719281</v>
+        <v>0.35893754486719282</v>
       </c>
       <c r="CO21" s="0">
         <v>1.0799612095565536</v>
@@ -7797,7 +7798,7 @@
         <v>0.10279413138958966</v>
       </c>
       <c r="F22" s="0">
-        <v>0.13199047373102626</v>
+        <v>0.13199047373102627</v>
       </c>
       <c r="G22" s="0">
         <v>0.13354700854700841</v>
@@ -7884,7 +7885,7 @@
         <v>1.0624801776086259</v>
       </c>
       <c r="AI22" s="0">
-        <v>0.83105300496604761</v>
+        <v>0.83105300496604762</v>
       </c>
       <c r="AJ22" s="0">
         <v>1.1971104231166139</v>
@@ -7911,7 +7912,7 @@
         <v>1.1015736766809718</v>
       </c>
       <c r="AR22" s="0">
-        <v>0.2367601246105917</v>
+        <v>0.23676012461059171</v>
       </c>
       <c r="AS22" s="0">
         <v>0.26455026455026431</v>
@@ -7950,7 +7951,7 @@
         <v>1.2058924289140105</v>
       </c>
       <c r="BE22" s="0">
-        <v>0.48445069542115909</v>
+        <v>0.4844506954211591</v>
       </c>
       <c r="BF22" s="0">
         <v>0.63862279605719785</v>
@@ -7986,7 +7987,7 @@
         <v>0.13962375073486172</v>
       </c>
       <c r="BQ22" s="0">
-        <v>0.93323761665470117</v>
+        <v>0.93323761665470118</v>
       </c>
       <c r="BR22" s="0">
         <v>1.0656333252603527</v>
@@ -8144,7 +8145,7 @@
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0.15698587127158597</v>
+        <v>0.15698587127158598</v>
       </c>
       <c r="B23" s="0">
         <v>0.17979595250041863</v>
@@ -8207,13 +8208,13 @@
         <v>0.53913366796802531</v>
       </c>
       <c r="V23" s="0">
-        <v>0.96507352941176749</v>
+        <v>0.9650735294117675</v>
       </c>
       <c r="W23" s="0">
         <v>0.49572649572649713</v>
       </c>
       <c r="X23" s="0">
-        <v>0.47375402690923007</v>
+        <v>0.47375402690923008</v>
       </c>
       <c r="Y23" s="0">
         <v>0.62893081761006464</v>
@@ -8294,7 +8295,7 @@
         <v>0.68874708801782836</v>
       </c>
       <c r="AY23" s="0">
-        <v>0.89652847994607598</v>
+        <v>0.89652847994607599</v>
       </c>
       <c r="AZ23" s="0">
         <v>0.32110658268494591</v>
@@ -8315,7 +8316,7 @@
         <v>0.54696046257227848</v>
       </c>
       <c r="BF23" s="0">
-        <v>0.47202554491184356</v>
+        <v>0.47202554491184357</v>
       </c>
       <c r="BG23" s="0">
         <v>0.98582871226124735</v>
@@ -8345,7 +8346,7 @@
         <v>0.13508949679162485</v>
       </c>
       <c r="BP23" s="0">
-        <v>0.21310993533215813</v>
+        <v>0.21310993533215814</v>
       </c>
       <c r="BQ23" s="0">
         <v>0.87341469251017245</v>
@@ -8411,7 +8412,7 @@
         <v>1.2005108556832726</v>
       </c>
       <c r="CL23" s="0">
-        <v>0.95364405709233568</v>
+        <v>0.95364405709233569</v>
       </c>
       <c r="CM23" s="0">
         <v>1.0993106018259768</v>
@@ -8465,7 +8466,7 @@
         <v>0.0074839095943721205</v>
       </c>
       <c r="DD23" s="0">
-        <v>0.006071645415907728</v>
+        <v>0.0060716454159077281</v>
       </c>
       <c r="DE23" s="0">
         <v>0.032221685194135742</v>
@@ -8477,7 +8478,7 @@
         <v>0.10162601626016289</v>
       </c>
       <c r="DH23" s="0">
-        <v>0.35650623885918103</v>
+        <v>0.35650623885918104</v>
       </c>
       <c r="DI23" s="0">
         <v>0</v>
@@ -8563,7 +8564,7 @@
         <v>0.25076623014767324</v>
       </c>
       <c r="T24" s="0">
-        <v>0.18438844499078041</v>
+        <v>0.18438844499078042</v>
       </c>
       <c r="U24" s="0">
         <v>0.669269380925822</v>
@@ -8578,7 +8579,7 @@
         <v>0.51165434906196661</v>
       </c>
       <c r="Y24" s="0">
-        <v>0.68134171907756746</v>
+        <v>0.68134171907756747</v>
       </c>
       <c r="Z24" s="0">
         <v>1.8302447952413619</v>
@@ -8593,7 +8594,7 @@
         <v>0.44917257683215089</v>
       </c>
       <c r="AD24" s="0">
-        <v>0.80894599095883823</v>
+        <v>0.80894599095883824</v>
       </c>
       <c r="AE24" s="0">
         <v>0.47814207650273183</v>
@@ -8934,7 +8935,7 @@
         <v>1.4399509803921555</v>
       </c>
       <c r="W25" s="0">
-        <v>0.66666666666666607</v>
+        <v>0.66666666666666608</v>
       </c>
       <c r="X25" s="0">
         <v>0.64430547659655057</v>
@@ -8994,7 +8995,7 @@
         <v>0.67696835908756381</v>
       </c>
       <c r="AQ25" s="0">
-        <v>1.373390557939913</v>
+        <v>1.3733905579399131</v>
       </c>
       <c r="AR25" s="0">
         <v>0.27414330218068511</v>
@@ -9027,7 +9028,7 @@
         <v>0.11534025374855815</v>
       </c>
       <c r="BB25" s="0">
-        <v>0.23654642223536348</v>
+        <v>0.23654642223536349</v>
       </c>
       <c r="BC25" s="0">
         <v>0.43169121381411846</v>
@@ -9096,13 +9097,13 @@
         <v>1.0236993409059028</v>
       </c>
       <c r="BY25" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="BZ25" s="0">
         <v>1.263823064770931</v>
       </c>
       <c r="CA25" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB25" s="0">
         <v>1.3123359580052483</v>
@@ -9114,7 +9115,7 @@
         <v>0.9487179487179479</v>
       </c>
       <c r="CE25" s="0">
-        <v>0.82539682539682468</v>
+        <v>0.82539682539682469</v>
       </c>
       <c r="CF25" s="0">
         <v>0.3454231433506042</v>
@@ -9141,7 +9142,7 @@
         <v>1.173840134153157</v>
       </c>
       <c r="CN25" s="0">
-        <v>0.58626465661641491</v>
+        <v>0.58626465661641492</v>
       </c>
       <c r="CO25" s="0">
         <v>1.1945693379176574</v>
@@ -9171,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="CX25" s="0">
-        <v>1.1665068712048567</v>
+        <v>1.1665068712048568</v>
       </c>
       <c r="CY25" s="0">
         <v>0.83475160061593257</v>
@@ -9242,7 +9243,7 @@
         <v>0.33877004617107859</v>
       </c>
       <c r="E26" s="0">
-        <v>0.2429679469208483</v>
+        <v>0.24296794692084831</v>
       </c>
       <c r="F26" s="0">
         <v>0.28406645433416516</v>
@@ -9272,10 +9273,10 @@
         <v>0.44652128764278259</v>
       </c>
       <c r="O26" s="0">
-        <v>0.28343550194449912</v>
+        <v>0.28343550194449913</v>
       </c>
       <c r="P26" s="0">
-        <v>0.29574020360575531</v>
+        <v>0.29574020360575532</v>
       </c>
       <c r="Q26" s="0">
         <v>0.25720164609053475</v>
@@ -9290,16 +9291,16 @@
         <v>0.22536365498873162</v>
       </c>
       <c r="U26" s="0">
-        <v>0.76222346160996401</v>
+        <v>0.76222346160996402</v>
       </c>
       <c r="V26" s="0">
         <v>1.087622549019607</v>
       </c>
       <c r="W26" s="0">
-        <v>0.66666666666666607</v>
+        <v>0.66666666666666608</v>
       </c>
       <c r="X26" s="0">
-        <v>0.79590676520750347</v>
+        <v>0.79590676520750348</v>
       </c>
       <c r="Y26" s="0">
         <v>0.75995807127882531</v>
@@ -9464,7 +9465,7 @@
         <v>1.2506582411795673</v>
       </c>
       <c r="CA26" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB26" s="0">
         <v>0.68241469816272904</v>
@@ -9554,7 +9555,7 @@
         <v>0.206435944140862</v>
       </c>
       <c r="DE26" s="0">
-        <v>0.19333011116481374</v>
+        <v>0.19333011116481375</v>
       </c>
       <c r="DF26" s="0">
         <v>0.61349693251533688</v>
@@ -9584,7 +9585,7 @@
         <v>0.065104166666666616</v>
       </c>
       <c r="DO26" s="0">
-        <v>0.40453074433656921</v>
+        <v>0.40453074433656922</v>
       </c>
       <c r="DP26" s="0">
         <v>0.35211267605633773</v>
@@ -9616,7 +9617,7 @@
         <v>0.30275507114744149</v>
       </c>
       <c r="I27" s="0">
-        <v>0.4872646733111845</v>
+        <v>0.48726467331118451</v>
       </c>
       <c r="J27" s="0">
         <v>0.50514738794040492</v>
@@ -9628,7 +9629,7 @@
         <v>0.37293553542887553</v>
       </c>
       <c r="M27" s="0">
-        <v>0.44352044352044317</v>
+        <v>0.44352044352044318</v>
       </c>
       <c r="N27" s="0">
         <v>0.46728971962616778</v>
@@ -9655,7 +9656,7 @@
         <v>0.7994050938836208</v>
       </c>
       <c r="V27" s="0">
-        <v>1.3020833333333321</v>
+        <v>1.3020833333333322</v>
       </c>
       <c r="W27" s="0">
         <v>0.88888888888888817</v>
@@ -9688,7 +9689,7 @@
         <v>0.28070175438596467</v>
       </c>
       <c r="AG27" s="0">
-        <v>1.1241889240983844</v>
+        <v>1.1241889240983845</v>
       </c>
       <c r="AH27" s="0">
         <v>1.4034253092293041</v>
@@ -9733,7 +9734,7 @@
         <v>1.1622156280909981</v>
       </c>
       <c r="AV27" s="0">
-        <v>1.0507489380728809</v>
+        <v>1.050748938072881</v>
       </c>
       <c r="AW27" s="0">
         <v>1.4442052386078206</v>
@@ -9757,13 +9758,13 @@
         <v>0.46554934823091204</v>
       </c>
       <c r="BD27" s="0">
-        <v>1.3155190133607388</v>
+        <v>1.3155190133607389</v>
       </c>
       <c r="BE27" s="0">
         <v>1.093920925144553</v>
       </c>
       <c r="BF27" s="0">
-        <v>0.93016798556157076</v>
+        <v>0.93016798556157077</v>
       </c>
       <c r="BG27" s="0">
         <v>1.2384473197781876</v>
@@ -9775,7 +9776,7 @@
         <v>1.2515689438766351</v>
       </c>
       <c r="BJ27" s="0">
-        <v>0.39432467293163775</v>
+        <v>0.39432467293163776</v>
       </c>
       <c r="BK27" s="0">
         <v>1.3119032900611294</v>
@@ -9811,7 +9812,7 @@
         <v>0.96363071184333149</v>
       </c>
       <c r="BV27" s="0">
-        <v>0.85176085176085103</v>
+        <v>0.85176085176085104</v>
       </c>
       <c r="BW27" s="0">
         <v>1.0233918128654962</v>
@@ -9820,7 +9821,7 @@
         <v>1.0236993409059028</v>
       </c>
       <c r="BY27" s="0">
-        <v>1.3238573021181705</v>
+        <v>1.3238573021181706</v>
       </c>
       <c r="BZ27" s="0">
         <v>1.4876250658241166</v>
@@ -9838,7 +9839,7 @@
         <v>1.5384615384615372</v>
       </c>
       <c r="CE27" s="0">
-        <v>0.82539682539682468</v>
+        <v>0.82539682539682469</v>
       </c>
       <c r="CF27" s="0">
         <v>0.51813471502590625</v>
@@ -9871,7 +9872,7 @@
         <v>1.2783214317200025</v>
       </c>
       <c r="CP27" s="0">
-        <v>1.1791981452612212</v>
+        <v>1.1791981452612213</v>
       </c>
       <c r="CQ27" s="0">
         <v>0.38469874295621986</v>
@@ -9910,7 +9911,7 @@
         <v>1.2277951933124336</v>
       </c>
       <c r="DC27" s="0">
-        <v>0.037419547971860471</v>
+        <v>0.037419547971860472</v>
       </c>
       <c r="DD27" s="0">
         <v>0.3035822707953853</v>
@@ -9934,7 +9935,7 @@
         <v>0</v>
       </c>
       <c r="DK27" s="0">
-        <v>2.9126213592232983</v>
+        <v>2.9126213592232984</v>
       </c>
       <c r="DL27" s="0">
         <v>0.17406440382941674</v>
@@ -10041,7 +10042,7 @@
         <v>0.85106382978723638</v>
       </c>
       <c r="AD28" s="0">
-        <v>1.0706638115631721</v>
+        <v>1.0706638115631722</v>
       </c>
       <c r="AE28" s="0">
         <v>0.61475409836065742</v>
@@ -10050,7 +10051,7 @@
         <v>0.21052631578947428</v>
       </c>
       <c r="AG28" s="0">
-        <v>1.2599969820431602</v>
+        <v>1.2599969820431603</v>
       </c>
       <c r="AH28" s="0">
         <v>1.4113542657786275</v>
@@ -10110,7 +10111,7 @@
         <v>0.61751265900951147</v>
       </c>
       <c r="BA28" s="0">
-        <v>0.28310789556464377</v>
+        <v>0.28310789556464378</v>
       </c>
       <c r="BB28" s="0">
         <v>0.32525133057362599</v>
@@ -10131,7 +10132,7 @@
         <v>1.3247073321010512</v>
       </c>
       <c r="BH28" s="0">
-        <v>0.85899152164212655</v>
+        <v>0.85899152164212656</v>
       </c>
       <c r="BI28" s="0">
         <v>1.255155101308951</v>
@@ -10155,7 +10156,7 @@
         <v>0.3489812000450308</v>
       </c>
       <c r="BP28" s="0">
-        <v>0.49970605526161221</v>
+        <v>0.49970605526161222</v>
       </c>
       <c r="BQ28" s="0">
         <v>1.3519980856664311</v>
@@ -10242,7 +10243,7 @@
         <v>0.026632576968147515</v>
       </c>
       <c r="CS28" s="0">
-        <v>2.7937490785788079</v>
+        <v>2.793749078578808</v>
       </c>
       <c r="CT28" s="0">
         <v>2.7099185689494139</v>
@@ -10263,10 +10264,10 @@
         <v>2.8527433341437796</v>
       </c>
       <c r="CZ28" s="0">
-        <v>0.5981511691136504</v>
+        <v>0.59815116911365041</v>
       </c>
       <c r="DA28" s="0">
-        <v>1.7771373679154709</v>
+        <v>1.777137367915471</v>
       </c>
       <c r="DB28" s="0">
         <v>2.2727272727272791</v>
@@ -10290,7 +10291,7 @@
         <v>4.1889483065953774</v>
       </c>
       <c r="DI28" s="0">
-        <v>3.1152647975077969</v>
+        <v>3.115264797507797</v>
       </c>
       <c r="DJ28" s="0">
         <v>0</v>
@@ -10436,7 +10437,7 @@
         <v>0.91264667535853894</v>
       </c>
       <c r="AO29" s="0">
-        <v>1.5131086142322085</v>
+        <v>1.5131086142322086</v>
       </c>
       <c r="AP29" s="0">
         <v>0.8977189109639433</v>
@@ -10472,7 +10473,7 @@
         <v>0.77189082376188645</v>
       </c>
       <c r="BA29" s="0">
-        <v>0.32504980601866384</v>
+        <v>0.32504980601866385</v>
       </c>
       <c r="BB29" s="0">
         <v>0.45338064261777999</v>
@@ -10544,7 +10545,7 @@
         <v>1.2200252419015554</v>
       </c>
       <c r="BY29" s="0">
-        <v>1.184503901895205</v>
+        <v>1.1845039018952051</v>
       </c>
       <c r="BZ29" s="0">
         <v>1.263823064770931</v>
@@ -10571,7 +10572,7 @@
         <v>1.2704603202741818</v>
       </c>
       <c r="CH29" s="0">
-        <v>0.71993286515613208</v>
+        <v>0.71993286515613209</v>
       </c>
       <c r="CI29" s="0">
         <v>1.1758180809761498</v>
@@ -10652,7 +10653,7 @@
         <v>4.9910873440285153</v>
       </c>
       <c r="DI29" s="0">
-        <v>2.4922118380062281</v>
+        <v>2.4922118380062282</v>
       </c>
       <c r="DJ29" s="0">
         <v>0.06775067750677502</v>
@@ -10687,7 +10688,7 @@
         <v>0.45662100456620963</v>
       </c>
       <c r="D30" s="0">
-        <v>0.69939622435319448</v>
+        <v>0.69939622435319449</v>
       </c>
       <c r="E30" s="0">
         <v>0.44544123602155522</v>
@@ -10765,7 +10766,7 @@
         <v>1.1347517730496444</v>
       </c>
       <c r="AD30" s="0">
-        <v>1.0706638115631681</v>
+        <v>1.0706638115631682</v>
       </c>
       <c r="AE30" s="0">
         <v>1.2295081967213104</v>
@@ -10816,7 +10817,7 @@
         <v>0.50083472454090106</v>
       </c>
       <c r="AU30" s="0">
-        <v>1.3724035608308593</v>
+        <v>1.3724035608308594</v>
       </c>
       <c r="AV30" s="0">
         <v>1.296668902302704</v>
@@ -10834,7 +10835,7 @@
         <v>0.83364208966283737</v>
       </c>
       <c r="BA30" s="0">
-        <v>0.32504980601866384</v>
+        <v>0.32504980601866385</v>
       </c>
       <c r="BB30" s="0">
         <v>0.48294894539720046</v>
@@ -10888,7 +10889,7 @@
         <v>1.3481876160490824</v>
       </c>
       <c r="BS30" s="0">
-        <v>1.147057635607253</v>
+        <v>1.1470576356072531</v>
       </c>
       <c r="BT30" s="0">
         <v>0.5130161960485029</v>
@@ -10897,7 +10898,7 @@
         <v>1.222671225779711</v>
       </c>
       <c r="BV30" s="0">
-        <v>1.3267813267813255</v>
+        <v>1.3267813267813256</v>
       </c>
       <c r="BW30" s="0">
         <v>1.3157894736842093</v>
@@ -11029,7 +11030,7 @@
         <v>0</v>
       </c>
       <c r="DN30" s="0">
-        <v>1.3020833333333321</v>
+        <v>1.3020833333333322</v>
       </c>
       <c r="DO30" s="0">
         <v>2.4271844660194151</v>
@@ -11049,7 +11050,7 @@
         <v>0.49491825011047236</v>
       </c>
       <c r="D31" s="0">
-        <v>0.72125235636423179</v>
+        <v>0.7212523563642318</v>
       </c>
       <c r="E31" s="0">
         <v>0.62922468305142765</v>
@@ -11070,7 +11071,7 @@
         <v>0.78010102947758742</v>
       </c>
       <c r="K31" s="0">
-        <v>1.0072215887495239</v>
+        <v>1.007221588749524</v>
       </c>
       <c r="L31" s="0">
         <v>0.39069437044929822</v>
@@ -11307,7 +11308,7 @@
         <v>1.2828153824322395</v>
       </c>
       <c r="CL31" s="0">
-        <v>1.2188960464822522</v>
+        <v>1.2188960464822523</v>
       </c>
       <c r="CM31" s="0">
         <v>1.0806782187441764</v>
@@ -11340,7 +11341,7 @@
         <v>4.1666666666666634</v>
       </c>
       <c r="CW31" s="0">
-        <v>0.63099138454071046</v>
+        <v>0.63099138454071047</v>
       </c>
       <c r="CX31" s="0">
         <v>3.4196228827101276</v>
@@ -11355,7 +11356,7 @@
         <v>3.3861671469740604</v>
       </c>
       <c r="DB31" s="0">
-        <v>4.1536050156739774</v>
+        <v>4.1536050156739775</v>
       </c>
       <c r="DC31" s="0">
         <v>0.63613231552162797</v>
@@ -11441,7 +11442,7 @@
         <v>0.7207207207207228</v>
       </c>
       <c r="N32" s="0">
-        <v>0.92419522326064651</v>
+        <v>0.92419522326064652</v>
       </c>
       <c r="O32" s="0">
         <v>0.69210994660866321</v>
@@ -11486,7 +11487,7 @@
         <v>0.96055589617821646</v>
       </c>
       <c r="AC32" s="0">
-        <v>0.80378250591016775</v>
+        <v>0.80378250591016776</v>
       </c>
       <c r="AD32" s="0">
         <v>1.1896264572924136</v>
@@ -11558,7 +11559,7 @@
         <v>0.93861924169445743</v>
       </c>
       <c r="BA32" s="0">
-        <v>0.63961413442382486</v>
+        <v>0.63961413442382487</v>
       </c>
       <c r="BB32" s="0">
         <v>0.57165385373546385</v>
@@ -11582,10 +11583,10 @@
         <v>0.97612672913878007</v>
       </c>
       <c r="BI32" s="0">
-        <v>1.4272906580598927</v>
+        <v>1.4272906580598928</v>
       </c>
       <c r="BJ32" s="0">
-        <v>0.83287267366869588</v>
+        <v>0.83287267366869589</v>
       </c>
       <c r="BK32" s="0">
         <v>1.3668521189642184</v>
@@ -11648,7 +11649,7 @@
         <v>1.2435897435897469</v>
       </c>
       <c r="CE32" s="0">
-        <v>1.3968253968254007</v>
+        <v>1.3968253968254008</v>
       </c>
       <c r="CF32" s="0">
         <v>1.0938399539435841</v>
@@ -11681,7 +11682,7 @@
         <v>1.2739134267830416</v>
       </c>
       <c r="CP32" s="0">
-        <v>1.3550785465883239</v>
+        <v>1.355078546588324</v>
       </c>
       <c r="CQ32" s="0">
         <v>3.2672301690507246</v>
@@ -11699,7 +11700,7 @@
         <v>3.8922155688622864</v>
       </c>
       <c r="CV32" s="0">
-        <v>3.4203980099502584</v>
+        <v>3.4203980099502585</v>
       </c>
       <c r="CW32" s="0">
         <v>1.0678315738381294</v>
@@ -11773,7 +11774,7 @@
         <v>0.70702607158638919</v>
       </c>
       <c r="D33" s="0">
-        <v>0.81414091741114047</v>
+        <v>0.81414091741114048</v>
       </c>
       <c r="E33" s="0">
         <v>0.71332897237018278</v>
@@ -11794,7 +11795,7 @@
         <v>1.1062088368821525</v>
       </c>
       <c r="K33" s="0">
-        <v>1.0072215887495239</v>
+        <v>1.007221588749524</v>
       </c>
       <c r="L33" s="0">
         <v>0.69259456579648304</v>
@@ -11806,7 +11807,7 @@
         <v>0.82035306334371683</v>
       </c>
       <c r="O33" s="0">
-        <v>0.76461670292004424</v>
+        <v>0.76461670292004425</v>
       </c>
       <c r="P33" s="0">
         <v>0.56304384917249573</v>
@@ -11890,10 +11891,10 @@
         <v>0.95658572479764448</v>
       </c>
       <c r="AQ33" s="0">
-        <v>0.75822603719599357</v>
+        <v>0.75822603719599358</v>
       </c>
       <c r="AR33" s="0">
-        <v>1.0965732087227404</v>
+        <v>1.0965732087227405</v>
       </c>
       <c r="AS33" s="0">
         <v>1.0582010582010573</v>
@@ -11908,7 +11909,7 @@
         <v>1.3115731425590569</v>
       </c>
       <c r="AW33" s="0">
-        <v>1.1302475780409031</v>
+        <v>1.1302475780409032</v>
       </c>
       <c r="AX33" s="0">
         <v>1.2863364732097629</v>
@@ -11929,7 +11930,7 @@
         <v>0.99881496529541125</v>
       </c>
       <c r="BD33" s="0">
-        <v>1.1305241521068849</v>
+        <v>1.130524152106885</v>
       </c>
       <c r="BE33" s="0">
         <v>1.1408032505078909</v>
@@ -11950,13 +11951,13 @@
         <v>0.84024322830292908</v>
       </c>
       <c r="BK33" s="0">
-        <v>1.4492753623188392</v>
+        <v>1.4492753623188393</v>
       </c>
       <c r="BL33" s="0">
         <v>1.2609858616736709</v>
       </c>
       <c r="BM33" s="0">
-        <v>1.2225505533344911</v>
+        <v>1.2225505533344912</v>
       </c>
       <c r="BN33" s="0">
         <v>1.2418503570319765</v>
@@ -11986,7 +11987,7 @@
         <v>1.2940212940212927</v>
       </c>
       <c r="BW33" s="0">
-        <v>1.3596491228070164</v>
+        <v>1.3596491228070165</v>
       </c>
       <c r="BX33" s="0">
         <v>1.2620950778291953</v>
@@ -12001,7 +12002,7 @@
         <v>1.1027568922305753</v>
       </c>
       <c r="CB33" s="0">
-        <v>1.5223097112860879</v>
+        <v>1.522309711286088</v>
       </c>
       <c r="CC33" s="0">
         <v>1.2498437695288078</v>
@@ -12043,7 +12044,7 @@
         <v>1.1284492638631747</v>
       </c>
       <c r="CP33" s="0">
-        <v>1.4230323380101519</v>
+        <v>1.423032338010152</v>
       </c>
       <c r="CQ33" s="0">
         <v>3.7169484178586876</v>
@@ -12067,7 +12068,7 @@
         <v>1.674554058973424</v>
       </c>
       <c r="CX33" s="0">
-        <v>2.8763183125599205</v>
+        <v>2.8763183125599206</v>
       </c>
       <c r="CY33" s="0">
         <v>3.1445011751357459</v>
@@ -12141,7 +12142,7 @@
         <v>0.81300813008130013</v>
       </c>
       <c r="F34" s="0">
-        <v>0.843591288628733</v>
+        <v>0.84359128862873301</v>
       </c>
       <c r="G34" s="0">
         <v>0.93482905982905906</v>
@@ -12156,7 +12157,7 @@
         <v>1.2660656052177239</v>
       </c>
       <c r="K34" s="0">
-        <v>1.0072215887495239</v>
+        <v>1.007221588749524</v>
       </c>
       <c r="L34" s="0">
         <v>0.79914757591901897</v>
@@ -12255,7 +12256,7 @@
         <v>1.0300429184549347</v>
       </c>
       <c r="AR34" s="0">
-        <v>1.0965732087227404</v>
+        <v>1.0965732087227405</v>
       </c>
       <c r="AS34" s="0">
         <v>1.3888888888888875</v>
@@ -12288,7 +12289,7 @@
         <v>0.85748078060319255</v>
       </c>
       <c r="BC34" s="0">
-        <v>1.1723379041814785</v>
+        <v>1.1723379041814786</v>
       </c>
       <c r="BD34" s="0">
         <v>1.1236724905789646</v>
@@ -12345,7 +12346,7 @@
         <v>1.3780955341415386</v>
       </c>
       <c r="BV34" s="0">
-        <v>1.3759213759213746</v>
+        <v>1.3759213759213747</v>
       </c>
       <c r="BW34" s="0">
         <v>1.286549707602338</v>
@@ -12354,7 +12355,7 @@
         <v>1.5565839293226742</v>
       </c>
       <c r="BY34" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="BZ34" s="0">
         <v>1.4086361242759333</v>
@@ -12387,7 +12388,7 @@
         <v>1.3976705490848573</v>
       </c>
       <c r="CJ34" s="0">
-        <v>1.3388150959308442</v>
+        <v>1.3388150959308443</v>
       </c>
       <c r="CK34" s="0">
         <v>1.1607776358734203</v>
@@ -12530,7 +12531,7 @@
         <v>1.0072689511941839</v>
       </c>
       <c r="O35" s="0">
-        <v>0.9096302155428112</v>
+        <v>0.90963021554281121</v>
       </c>
       <c r="P35" s="0">
         <v>0.76778706705340327</v>
@@ -12641,7 +12642,7 @@
         <v>1.4627569935962239</v>
       </c>
       <c r="AZ35" s="0">
-        <v>1.0682969000864508</v>
+        <v>1.0682969000864509</v>
       </c>
       <c r="BA35" s="0">
         <v>0.82835273146691757</v>
@@ -12749,7 +12750,7 @@
         <v>1.5751525235718233</v>
       </c>
       <c r="CJ35" s="0">
-        <v>1.5285684166139561</v>
+        <v>1.5285684166139562</v>
       </c>
       <c r="CK35" s="0">
         <v>1.206187029941818</v>
@@ -12886,10 +12887,10 @@
         <v>1.0122535961640906</v>
       </c>
       <c r="M36" s="0">
-        <v>0.91476091476091403</v>
+        <v>0.91476091476091404</v>
       </c>
       <c r="N36" s="0">
-        <v>1.3084112149532698</v>
+        <v>1.3084112149532699</v>
       </c>
       <c r="O36" s="0">
         <v>1.1007843912728221</v>
@@ -13006,7 +13007,7 @@
         <v>1.1856243052982576</v>
       </c>
       <c r="BA36" s="0">
-        <v>1.0066058508965074</v>
+        <v>1.0066058508965075</v>
       </c>
       <c r="BB36" s="0">
         <v>0.8279124778237722</v>
@@ -13069,7 +13070,7 @@
         <v>1.3470106724691731</v>
       </c>
       <c r="BV36" s="0">
-        <v>1.3104013104013092</v>
+        <v>1.3104013104013093</v>
       </c>
       <c r="BW36" s="0">
         <v>1.3304093567251449</v>
@@ -13198,7 +13199,7 @@
         <v>4.0469973890339386</v>
       </c>
       <c r="DM36" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="DN36" s="0">
         <v>3.3854166666666639</v>
@@ -13224,7 +13225,7 @@
         <v>1.1228587820670428</v>
       </c>
       <c r="E37" s="0">
-        <v>1.0248263402174242</v>
+        <v>1.0248263402174243</v>
       </c>
       <c r="F37" s="0">
         <v>1.1793061892054737</v>
@@ -13266,7 +13267,7 @@
         <v>1.2855831037649208</v>
       </c>
       <c r="S37" s="0">
-        <v>1.0959413021268682</v>
+        <v>1.0959413021268683</v>
       </c>
       <c r="T37" s="0">
         <v>1.3112067199344384</v>
@@ -13431,7 +13432,7 @@
         <v>1.3677339135840831</v>
       </c>
       <c r="BV37" s="0">
-        <v>1.3759213759213746</v>
+        <v>1.3759213759213747</v>
       </c>
       <c r="BW37" s="0">
         <v>1.154970760233917</v>
@@ -13577,7 +13578,7 @@
         <v>1.0022944088878221</v>
       </c>
       <c r="B38" s="0">
-        <v>1.1498578357584956</v>
+        <v>1.1498578357584957</v>
       </c>
       <c r="C38" s="0">
         <v>1.0399175136249883</v>
@@ -13718,7 +13719,7 @@
         <v>1.274312541918184</v>
       </c>
       <c r="AW38" s="0">
-        <v>0.80731969860065111</v>
+        <v>0.80731969860065112</v>
       </c>
       <c r="AX38" s="0">
         <v>1.195178770383883</v>
@@ -13736,7 +13737,7 @@
         <v>1.1334516065444582</v>
       </c>
       <c r="BC38" s="0">
-        <v>1.3077704418486626</v>
+        <v>1.3077704418486627</v>
       </c>
       <c r="BD38" s="0">
         <v>0.63035286056869211</v>
@@ -13751,7 +13752,7 @@
         <v>0.98582871226125102</v>
       </c>
       <c r="BH38" s="0">
-        <v>1.2884872824631945</v>
+        <v>1.2884872824631946</v>
       </c>
       <c r="BI38" s="0">
         <v>1.0184687107764097</v>
@@ -13829,7 +13830,7 @@
         <v>1.2054600248183025</v>
       </c>
       <c r="CH38" s="0">
-        <v>1.1748597676781138</v>
+        <v>1.1748597676781139</v>
       </c>
       <c r="CI38" s="0">
         <v>1.1092623405435458</v>
@@ -13886,7 +13887,7 @@
         <v>2.3926046764546101</v>
       </c>
       <c r="DA38" s="0">
-        <v>1.1527377521613908</v>
+        <v>1.1527377521613909</v>
       </c>
       <c r="DB38" s="0">
         <v>0.83594566353187583</v>
@@ -13972,7 +13973,7 @@
         <v>1.0300124311845134</v>
       </c>
       <c r="M39" s="0">
-        <v>1.4830214830214818</v>
+        <v>1.4830214830214819</v>
       </c>
       <c r="N39" s="0">
         <v>1.2045690550363437</v>
@@ -13984,7 +13985,7 @@
         <v>1.1147130751293852</v>
       </c>
       <c r="Q39" s="0">
-        <v>1.5946502057613154</v>
+        <v>1.5946502057613155</v>
       </c>
       <c r="R39" s="0">
         <v>0.87235996326905341</v>
@@ -14092,10 +14093,10 @@
         <v>1.3955786093614906</v>
       </c>
       <c r="BA39" s="0">
-        <v>1.0066058508965074</v>
+        <v>1.0066058508965075</v>
       </c>
       <c r="BB39" s="0">
-        <v>1.0250344963532418</v>
+        <v>1.0250344963532419</v>
       </c>
       <c r="BC39" s="0">
         <v>1.328931775859149</v>
@@ -14113,7 +14114,7 @@
         <v>0.9488601355514471</v>
       </c>
       <c r="BH39" s="0">
-        <v>1.2717536813922345</v>
+        <v>1.2717536813922346</v>
       </c>
       <c r="BI39" s="0">
         <v>1.0399856553702698</v>
@@ -14164,7 +14165,7 @@
         <v>1.1078390127611826</v>
       </c>
       <c r="BY39" s="0">
-        <v>0.85005574136008843</v>
+        <v>0.85005574136008844</v>
       </c>
       <c r="BZ39" s="0">
         <v>0.81621906266455957</v>
@@ -14433,7 +14434,7 @@
         <v>1.1243386243386233</v>
       </c>
       <c r="AT40" s="0">
-        <v>1.8363939899833039</v>
+        <v>1.836393989983304</v>
       </c>
       <c r="AU40" s="0">
         <v>0.61819980217606274</v>
@@ -14454,10 +14455,10 @@
         <v>1.5005557613931071</v>
       </c>
       <c r="BA40" s="0">
-        <v>0.97514941805599153</v>
+        <v>0.97514941805599154</v>
       </c>
       <c r="BB40" s="0">
-        <v>1.1038833037650297</v>
+        <v>1.1038833037650298</v>
       </c>
       <c r="BC40" s="0">
         <v>1.3924157778906372</v>
@@ -14484,7 +14485,7 @@
         <v>1.4372581536760627</v>
       </c>
       <c r="BK40" s="0">
-        <v>0.7761522082560609</v>
+        <v>0.77615220825606091</v>
       </c>
       <c r="BL40" s="0">
         <v>0.93618647306075575</v>
@@ -14544,7 +14545,7 @@
         <v>0.74358974358974284</v>
       </c>
       <c r="CE40" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="CF40" s="0">
         <v>1.3241220495106494</v>
@@ -14649,7 +14650,7 @@
         <v>3.9886039886039852</v>
       </c>
       <c r="DN40" s="0">
-        <v>0.7161458333333327</v>
+        <v>0.71614583333333271</v>
       </c>
       <c r="DO40" s="0">
         <v>0.5663430420711969</v>
@@ -14660,7 +14661,7 @@
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>1.304190315179325</v>
+        <v>1.3041903151793251</v>
       </c>
       <c r="B41" s="0">
         <v>1.2752968723866858</v>
@@ -14876,10 +14877,10 @@
         <v>1.3228186212159745</v>
       </c>
       <c r="BU41" s="0">
-        <v>1.1397782613200695</v>
+        <v>1.1397782613200696</v>
       </c>
       <c r="BV41" s="0">
-        <v>1.2612612612612601</v>
+        <v>1.2612612612612602</v>
       </c>
       <c r="BW41" s="0">
         <v>0.99415204678362479</v>
@@ -14939,7 +14940,7 @@
         <v>0.52014458256193197</v>
       </c>
       <c r="CP41" s="0">
-        <v>0.8274373426070265</v>
+        <v>0.82743734260702651</v>
       </c>
       <c r="CQ41" s="0">
         <v>0.34135240572171621</v>
@@ -15151,13 +15152,13 @@
         <v>0.2718168812589411</v>
       </c>
       <c r="AR42" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="AS42" s="0">
         <v>1.0582010582010573</v>
       </c>
       <c r="AT42" s="0">
-        <v>1.8363939899833039</v>
+        <v>1.836393989983304</v>
       </c>
       <c r="AU42" s="0">
         <v>0.62438180019782341</v>
@@ -15187,7 +15188,7 @@
         <v>1.3246995090570497</v>
       </c>
       <c r="BD42" s="0">
-        <v>0.54813292223364118</v>
+        <v>0.54813292223364119</v>
       </c>
       <c r="BE42" s="0">
         <v>1.0626660415689941</v>
@@ -15214,7 +15215,7 @@
         <v>0.90434339574576406</v>
       </c>
       <c r="BM42" s="0">
-        <v>1.2225505533344911</v>
+        <v>1.2225505533344912</v>
       </c>
       <c r="BN42" s="0">
         <v>1.2004553451309106</v>
@@ -15268,7 +15269,7 @@
         <v>0.53846153846153799</v>
       </c>
       <c r="CE42" s="0">
-        <v>0.82539682539682468</v>
+        <v>0.82539682539682469</v>
       </c>
       <c r="CF42" s="0">
         <v>1.3816925734024168</v>
@@ -15286,7 +15287,7 @@
         <v>0.95930845456462066</v>
       </c>
       <c r="CK42" s="0">
-        <v>0.61018873279409624</v>
+        <v>0.61018873279409625</v>
       </c>
       <c r="CL42" s="0">
         <v>0.89996210685865785</v>
@@ -15435,7 +15436,7 @@
         <v>1.3888888888888875</v>
       </c>
       <c r="R43" s="0">
-        <v>1.7906336088154255</v>
+        <v>1.7906336088154256</v>
       </c>
       <c r="S43" s="0">
         <v>1.3420637131977327</v>
@@ -15528,7 +15529,7 @@
         <v>0.9166107757657046</v>
       </c>
       <c r="AW43" s="0">
-        <v>0.39468963042698207</v>
+        <v>0.39468963042698208</v>
       </c>
       <c r="AX43" s="0">
         <v>0.73939025625443067</v>
@@ -15552,7 +15553,7 @@
         <v>0.5001712915381975</v>
       </c>
       <c r="BE43" s="0">
-        <v>0.82825441475230432</v>
+        <v>0.82825441475230433</v>
       </c>
       <c r="BF43" s="0">
         <v>1.2494793835901696</v>
@@ -15630,7 +15631,7 @@
         <v>0.5897435897435892</v>
       </c>
       <c r="CE43" s="0">
-        <v>0.82539682539682468</v>
+        <v>0.82539682539682469</v>
       </c>
       <c r="CF43" s="0">
         <v>0.92112838226827776</v>
@@ -15645,7 +15646,7 @@
         <v>0.61009428729894566</v>
       </c>
       <c r="CJ43" s="0">
-        <v>1.1279780729496089</v>
+        <v>1.127978072949609</v>
       </c>
       <c r="CK43" s="0">
         <v>0.52220803178657538</v>
@@ -15729,7 +15730,7 @@
         <v>0</v>
       </c>
       <c r="DL43" s="0">
-        <v>0.30461270670147927</v>
+        <v>0.30461270670147928</v>
       </c>
       <c r="DM43" s="0">
         <v>4.273504273504269</v>
@@ -15773,7 +15774,7 @@
         <v>1.4673311184939077</v>
       </c>
       <c r="J44" s="0">
-        <v>1.1957286271500724</v>
+        <v>1.1957286271500725</v>
       </c>
       <c r="K44" s="0">
         <v>1.2732801216267569</v>
@@ -15920,7 +15921,7 @@
         <v>1.0967652367069267</v>
       </c>
       <c r="BG44" s="0">
-        <v>0.48059149722735633</v>
+        <v>0.48059149722735634</v>
       </c>
       <c r="BH44" s="0">
         <v>1.2103971441320829</v>
@@ -15995,7 +15996,7 @@
         <v>0.7619047619047612</v>
       </c>
       <c r="CF44" s="0">
-        <v>0.80598733448474313</v>
+        <v>0.80598733448474314</v>
       </c>
       <c r="CG44" s="0">
         <v>0.71500325001477216</v>
@@ -16046,7 +16047,7 @@
         <v>0</v>
       </c>
       <c r="CW44" s="0">
-        <v>0.48537798810823884</v>
+        <v>0.48537798810823885</v>
       </c>
       <c r="CX44" s="0">
         <v>0</v>
@@ -16521,7 +16522,7 @@
         <v>0.77160493827160992</v>
       </c>
       <c r="R46" s="0">
-        <v>1.2855831037649303</v>
+        <v>1.2855831037649304</v>
       </c>
       <c r="S46" s="0">
         <v>1.2352558744311402</v>
@@ -16602,7 +16603,7 @@
         <v>1.383177570093467</v>
       </c>
       <c r="AS46" s="0">
-        <v>0.79365079365079882</v>
+        <v>0.79365079365079883</v>
       </c>
       <c r="AT46" s="0">
         <v>1.2799109627156455</v>
@@ -16722,7 +16723,7 @@
         <v>0.74841681059298126</v>
       </c>
       <c r="CG46" s="0">
-        <v>0.62045736571530274</v>
+        <v>0.62045736571530275</v>
       </c>
       <c r="CH46" s="0">
         <v>1.2101938960293352</v>
@@ -16734,7 +16735,7 @@
         <v>0.73792958043432899</v>
       </c>
       <c r="CK46" s="0">
-        <v>0.32070384560806225</v>
+        <v>0.32070384560806226</v>
       </c>
       <c r="CL46" s="0">
         <v>0.54313502589365015</v>
@@ -16868,7 +16869,7 @@
         <v>1.3851891315929661</v>
       </c>
       <c r="M47" s="0">
-        <v>1.2889812889812879</v>
+        <v>1.288981288981288</v>
       </c>
       <c r="N47" s="0">
         <v>1.2668743509864995</v>
@@ -16937,7 +16938,7 @@
         <v>0.31417857504814001</v>
       </c>
       <c r="AJ47" s="0">
-        <v>0.25799793601651166</v>
+        <v>0.25799793601651167</v>
       </c>
       <c r="AK47" s="0">
         <v>1.3594829507466002</v>
@@ -17009,7 +17010,7 @@
         <v>0.29574861367837307</v>
       </c>
       <c r="BH47" s="0">
-        <v>0.82552431950022231</v>
+        <v>0.82552431950022232</v>
       </c>
       <c r="BI47" s="0">
         <v>0.34785727093419372</v>
@@ -17054,7 +17055,7 @@
         <v>0.68796068796068732</v>
       </c>
       <c r="BW47" s="0">
-        <v>0.73099415204678297</v>
+        <v>0.73099415204678298</v>
       </c>
       <c r="BX47" s="0">
         <v>0.51886130977422473</v>
@@ -17075,7 +17076,7 @@
         <v>0.74990626171728458</v>
       </c>
       <c r="CD47" s="0">
-        <v>0.20512820512820495</v>
+        <v>0.20512820512820496</v>
       </c>
       <c r="CE47" s="0">
         <v>0.44444444444444409</v>
@@ -17206,7 +17207,7 @@
         <v>1.2348714586236089</v>
       </c>
       <c r="E48" s="0">
-        <v>1.2615643397813276</v>
+        <v>1.2615643397813277</v>
       </c>
       <c r="F48" s="0">
         <v>1.1678287567071237</v>
@@ -17305,7 +17306,7 @@
         <v>1.1811901047470459</v>
       </c>
       <c r="AL48" s="0">
-        <v>0.9157154833301081</v>
+        <v>0.91571548333010811</v>
       </c>
       <c r="AM48" s="0">
         <v>0.092678405931417893</v>
@@ -17383,7 +17384,7 @@
         <v>0.25413833367676331</v>
       </c>
       <c r="BL48" s="0">
-        <v>0.40759138963189367</v>
+        <v>0.40759138963189368</v>
       </c>
       <c r="BM48" s="0">
         <v>0.52146706066400095</v>
@@ -17392,7 +17393,7 @@
         <v>0.42429887198592531</v>
       </c>
       <c r="BO48" s="0">
-        <v>1.3846673421141495</v>
+        <v>1.3846673421141496</v>
       </c>
       <c r="BP48" s="0">
         <v>1.1243386243386233</v>
@@ -17404,7 +17405,7 @@
         <v>0.15338661499959622</v>
       </c>
       <c r="BS48" s="0">
-        <v>0.58968455915020745</v>
+        <v>0.58968455915020746</v>
       </c>
       <c r="BT48" s="0">
         <v>1.1489866870177212</v>
@@ -17470,7 +17471,7 @@
         <v>0.77769801387891779</v>
       </c>
       <c r="CO48" s="0">
-        <v>0.13224014810896575</v>
+        <v>0.13224014810896576</v>
       </c>
       <c r="CP48" s="0">
         <v>0.27980972938401866</v>
@@ -17601,7 +17602,7 @@
         <v>1.2326148572935196</v>
       </c>
       <c r="P49" s="0">
-        <v>1.2398339305010508</v>
+        <v>1.2398339305010509</v>
       </c>
       <c r="Q49" s="0">
         <v>0.72016460905349722</v>
@@ -17622,7 +17623,7 @@
         <v>0.18382352941176455</v>
       </c>
       <c r="W49" s="0">
-        <v>0.75213675213675157</v>
+        <v>0.75213675213675158</v>
       </c>
       <c r="X49" s="0">
         <v>0.64430547659655057</v>
@@ -17640,7 +17641,7 @@
         <v>1.1036174126302871</v>
       </c>
       <c r="AC49" s="0">
-        <v>0.78014184397163044</v>
+        <v>0.78014184397163045</v>
       </c>
       <c r="AD49" s="0">
         <v>0.40447299547941912</v>
@@ -17700,7 +17701,7 @@
         <v>0.38751024666517592</v>
       </c>
       <c r="AW49" s="0">
-        <v>0.14352350197344801</v>
+        <v>0.14352350197344802</v>
       </c>
       <c r="AX49" s="0">
         <v>0.29373037577230804</v>
@@ -17942,7 +17943,7 @@
         <v>1.0495509133111305</v>
       </c>
       <c r="I50" s="0">
-        <v>0.94684385382059721</v>
+        <v>0.94684385382059722</v>
       </c>
       <c r="J50" s="0">
         <v>0.9527463392800043</v>
@@ -18038,7 +18039,7 @@
         <v>0.82572794437201136</v>
       </c>
       <c r="AO50" s="0">
-        <v>0.089887640449438116</v>
+        <v>0.089887640449438117</v>
       </c>
       <c r="AP50" s="0">
         <v>0.60338484179543728</v>
@@ -18080,7 +18081,7 @@
         <v>1.1433077074709235</v>
       </c>
       <c r="BC50" s="0">
-        <v>0.87184696123243532</v>
+        <v>0.87184696123243533</v>
       </c>
       <c r="BD50" s="0">
         <v>0.10277492291880772</v>
@@ -18182,7 +18183,7 @@
         <v>0.56925996204933538</v>
       </c>
       <c r="CK50" s="0">
-        <v>0.17879948914431656</v>
+        <v>0.17879948914431657</v>
       </c>
       <c r="CL50" s="0">
         <v>0.23683213338385734</v>
@@ -18310,7 +18311,7 @@
         <v>0.72255259287678175</v>
       </c>
       <c r="K51" s="0">
-        <v>1.0072215887495239</v>
+        <v>1.007221588749524</v>
       </c>
       <c r="L51" s="0">
         <v>1.1010477712662039</v>
@@ -18556,7 +18557,7 @@
         <v>0.34697296003828637</v>
       </c>
       <c r="CO51" s="0">
-        <v>0.066120074054482877</v>
+        <v>0.066120074054482878</v>
       </c>
       <c r="CP51" s="0">
         <v>0.19186952872046992</v>
@@ -18651,7 +18652,7 @@
         <v>0.98394461629105823</v>
       </c>
       <c r="D52" s="0">
-        <v>0.81414091741114047</v>
+        <v>0.81414091741114048</v>
       </c>
       <c r="E52" s="0">
         <v>0.87219262997227598</v>
@@ -18900,10 +18901,10 @@
         <v>0.706682567024424</v>
       </c>
       <c r="CI52" s="0">
-        <v>0.26622296173044901</v>
+        <v>0.26622296173044902</v>
       </c>
       <c r="CJ52" s="0">
-        <v>0.37950664136622358</v>
+        <v>0.37950664136622359</v>
       </c>
       <c r="CK52" s="0">
         <v>0.10500922378317004</v>
@@ -19031,7 +19032,7 @@
         <v>0.60908084163898069</v>
       </c>
       <c r="J53" s="0">
-        <v>0.70336978067651323</v>
+        <v>0.70336978067651324</v>
       </c>
       <c r="K53" s="0">
         <v>0.8741923223109076</v>
@@ -19040,7 +19041,7 @@
         <v>1.0832889362457814</v>
       </c>
       <c r="M53" s="0">
-        <v>0.91476091476091403</v>
+        <v>0.91476091476091404</v>
       </c>
       <c r="N53" s="0">
         <v>0.66458982346832762</v>
@@ -19181,7 +19182,7 @@
         <v>0.061614294516327731</v>
       </c>
       <c r="BH53" s="0">
-        <v>0.32909415439535888</v>
+        <v>0.32909415439535889</v>
       </c>
       <c r="BI53" s="0">
         <v>0.093240093240093164</v>
@@ -19193,7 +19194,7 @@
         <v>0.16484648670925187</v>
       </c>
       <c r="BL53" s="0">
-        <v>0.16558400203795678</v>
+        <v>0.16558400203795679</v>
       </c>
       <c r="BM53" s="0">
         <v>0.23755721652471154</v>
@@ -19241,7 +19242,7 @@
         <v>0.45112781954887177</v>
       </c>
       <c r="CB53" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC53" s="0">
         <v>0.38745156855393043</v>
@@ -19369,19 +19370,19 @@
         <v>0.8533590951173361</v>
       </c>
       <c r="B54" s="0">
-        <v>0.8571667502926904</v>
+        <v>0.85716675029269041</v>
       </c>
       <c r="C54" s="0">
         <v>0.84843128590366701</v>
       </c>
       <c r="D54" s="0">
-        <v>0.77862470289320473</v>
+        <v>0.77862470289320474</v>
       </c>
       <c r="E54" s="0">
         <v>0.87530760365074833</v>
       </c>
       <c r="F54" s="0">
-        <v>0.69725402427476912</v>
+        <v>0.69725402427476913</v>
       </c>
       <c r="G54" s="0">
         <v>0.88141025641025561</v>
@@ -19423,7 +19424,7 @@
         <v>0.79873688121110731</v>
       </c>
       <c r="T54" s="0">
-        <v>0.69657856996517042</v>
+        <v>0.69657856996517043</v>
       </c>
       <c r="U54" s="0">
         <v>0.35322550659973939</v>
@@ -19531,7 +19532,7 @@
         <v>0.50363974944980494</v>
       </c>
       <c r="BD54" s="0">
-        <v>0.054813292223364118</v>
+        <v>0.054813292223364119</v>
       </c>
       <c r="BE54" s="0">
         <v>0.10939209251445528</v>
@@ -19770,7 +19771,7 @@
         <v>0.612668743509869</v>
       </c>
       <c r="O55" s="0">
-        <v>0.70529299321073557</v>
+        <v>0.70529299321073558</v>
       </c>
       <c r="P55" s="0">
         <v>0.79053631348462094</v>
@@ -19779,10 +19780,10 @@
         <v>0.56584362139918065</v>
       </c>
       <c r="R55" s="0">
-        <v>0.41322314049587044</v>
+        <v>0.41322314049587045</v>
       </c>
       <c r="S55" s="0">
-        <v>0.74765487136621644</v>
+        <v>0.74765487136621645</v>
       </c>
       <c r="T55" s="0">
         <v>0.63511575496824835</v>
@@ -19812,7 +19813,7 @@
         <v>0.53137134682199405</v>
       </c>
       <c r="AC55" s="0">
-        <v>0.30732860520094762</v>
+        <v>0.30732860520094763</v>
       </c>
       <c r="AD55" s="0">
         <v>0.16654770402093852</v>
@@ -19830,7 +19831,7 @@
         <v>0.015857913098636323</v>
       </c>
       <c r="AI55" s="0">
-        <v>0.040539170973953847</v>
+        <v>0.040539170973953848</v>
       </c>
       <c r="AJ55" s="0">
         <v>0.020639834881321085</v>
@@ -19851,7 +19852,7 @@
         <v>0</v>
       </c>
       <c r="AP55" s="0">
-        <v>0.25018395879323196</v>
+        <v>0.25018395879323197</v>
       </c>
       <c r="AQ55" s="0">
         <v>0</v>
@@ -19911,7 +19912,7 @@
         <v>0.043033889187735617</v>
       </c>
       <c r="BJ55" s="0">
-        <v>0.68546158098397358</v>
+        <v>0.68546158098397359</v>
       </c>
       <c r="BK55" s="0">
         <v>0.082423243354626544</v>
@@ -19989,7 +19990,7 @@
         <v>0.077648363838048198</v>
       </c>
       <c r="CJ55" s="0">
-        <v>0.21083702298123685</v>
+        <v>0.21083702298123686</v>
       </c>
       <c r="CK55" s="0">
         <v>0.028380871292748872</v>
@@ -20093,7 +20094,7 @@
         <v>0.7164996175985181</v>
       </c>
       <c r="B56" s="0">
-        <v>0.62719518314099298</v>
+        <v>0.62719518314099299</v>
       </c>
       <c r="C56" s="0">
         <v>0.72175578141110552</v>
@@ -20126,7 +20127,7 @@
         <v>0.46172971053098877</v>
       </c>
       <c r="M56" s="0">
-        <v>0.49896049896049854</v>
+        <v>0.49896049896049855</v>
       </c>
       <c r="N56" s="0">
         <v>0.45690550363447519</v>
@@ -20249,7 +20250,7 @@
         <v>0.78641082101289639</v>
       </c>
       <c r="BB56" s="0">
-        <v>0.58150995466193522</v>
+        <v>0.58150995466193523</v>
       </c>
       <c r="BC56" s="0">
         <v>0.34281361097003521</v>
@@ -20327,7 +20328,7 @@
         <v>0.30075187969924788</v>
       </c>
       <c r="CB56" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC56" s="0">
         <v>0.1749781277340331</v>
@@ -20509,7 +20510,7 @@
         <v>0.39936844060555365</v>
       </c>
       <c r="T57" s="0">
-        <v>0.49853172164173964</v>
+        <v>0.49853172164173965</v>
       </c>
       <c r="U57" s="0">
         <v>0.20449897750511228</v>
@@ -20539,7 +20540,7 @@
         <v>0.26004728132387683</v>
       </c>
       <c r="AD57" s="0">
-        <v>0.071377587437544548</v>
+        <v>0.071377587437544549</v>
       </c>
       <c r="AE57" s="0">
         <v>0.20491803278688506</v>
@@ -20659,7 +20660,7 @@
         <v>0.071787508973438552</v>
       </c>
       <c r="BR57" s="0">
-        <v>0.024218939210462562</v>
+        <v>0.024218939210462563</v>
       </c>
       <c r="BS57" s="0">
         <v>0.1211680600993577</v>
@@ -20683,13 +20684,13 @@
         <v>0.069676700111482651</v>
       </c>
       <c r="BZ57" s="0">
-        <v>0.026329647182727726</v>
+        <v>0.026329647182727727</v>
       </c>
       <c r="CA57" s="0">
         <v>0.45112781954887177</v>
       </c>
       <c r="CB57" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC57" s="0">
         <v>0.19997500312460925</v>
@@ -20925,13 +20926,13 @@
         <v>0.35658569199910822</v>
       </c>
       <c r="AL58" s="0">
-        <v>0.22570452053911116</v>
+        <v>0.22570452053911117</v>
       </c>
       <c r="AM58" s="0">
         <v>0</v>
       </c>
       <c r="AN58" s="0">
-        <v>0.21729682746631881</v>
+        <v>0.21729682746631882</v>
       </c>
       <c r="AO58" s="0">
         <v>0.014981273408239688</v>
@@ -21081,7 +21082,7 @@
         <v>0.014190435646374332</v>
       </c>
       <c r="CL58" s="0">
-        <v>0.047366426676771461</v>
+        <v>0.047366426676771462</v>
       </c>
       <c r="CM58" s="0">
         <v>0</v>
@@ -21254,7 +21255,7 @@
         <v>0</v>
       </c>
       <c r="AA59" s="0">
-        <v>0.23453532688361164</v>
+        <v>0.23453532688361165</v>
       </c>
       <c r="AB59" s="0">
         <v>0.40874718986306935</v>
@@ -21293,7 +21294,7 @@
         <v>0.030892801977139301</v>
       </c>
       <c r="AN59" s="0">
-        <v>0.17383746197305502</v>
+        <v>0.17383746197305503</v>
       </c>
       <c r="AO59" s="0">
         <v>0</v>
@@ -21356,7 +21357,7 @@
         <v>0.13386880856760361</v>
       </c>
       <c r="BI59" s="0">
-        <v>0.032275416890801475</v>
+        <v>0.032275416890801476</v>
       </c>
       <c r="BJ59" s="0">
         <v>0.25796941219826769</v>
@@ -21374,7 +21375,7 @@
         <v>0.062092517851598833</v>
       </c>
       <c r="BO59" s="0">
-        <v>0.4277834065068104</v>
+        <v>0.42778340650681041</v>
       </c>
       <c r="BP59" s="0">
         <v>0.21310993533215736</v>
@@ -21410,10 +21411,10 @@
         <v>0.013164823591363863</v>
       </c>
       <c r="CA59" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB59" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC59" s="0">
         <v>0.18747656542932115</v>
@@ -21440,7 +21441,7 @@
         <v>0.10541851149061765</v>
       </c>
       <c r="CK59" s="0">
-        <v>0.017028522775649198</v>
+        <v>0.017028522775649199</v>
       </c>
       <c r="CL59" s="0">
         <v>0.050524188455222892</v>
@@ -21550,7 +21551,7 @@
         <v>0.25954156763106828</v>
       </c>
       <c r="E60" s="0">
-        <v>0.32395726256113105</v>
+        <v>0.32395726256113106</v>
       </c>
       <c r="F60" s="0">
         <v>0.36440848182261593</v>
@@ -21604,7 +21605,7 @@
         <v>0.015318627450980378</v>
       </c>
       <c r="W60" s="0">
-        <v>0.085470085470085388</v>
+        <v>0.085470085470085389</v>
       </c>
       <c r="X60" s="0">
         <v>0.11370096645821479</v>
@@ -21733,7 +21734,7 @@
         <v>0.075323019873689029</v>
       </c>
       <c r="BN60" s="0">
-        <v>0.031046258925799416</v>
+        <v>0.031046258925799417</v>
       </c>
       <c r="BO60" s="0">
         <v>0.405268490374873</v>
@@ -21775,7 +21776,7 @@
         <v>0.2005012531328319</v>
       </c>
       <c r="CB60" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC60" s="0">
         <v>0.13748281464816886</v>
@@ -21912,7 +21913,7 @@
         <v>0.24314946862279027</v>
       </c>
       <c r="E61" s="0">
-        <v>0.33018720991807587</v>
+        <v>0.33018720991807588</v>
       </c>
       <c r="F61" s="0">
         <v>0.25250351496370238</v>
@@ -21981,7 +21982,7 @@
         <v>0.058633831720902911</v>
       </c>
       <c r="AB61" s="0">
-        <v>0.20437359493153467</v>
+        <v>0.20437359493153468</v>
       </c>
       <c r="AC61" s="0">
         <v>0.070921985815602773</v>
@@ -22307,7 +22308,7 @@
         <v>0.23070331553622023</v>
       </c>
       <c r="P62" s="0">
-        <v>0.30711482682136126</v>
+        <v>0.30711482682136127</v>
       </c>
       <c r="Q62" s="0">
         <v>0.25720164609053475</v>
@@ -22316,7 +22317,7 @@
         <v>0</v>
       </c>
       <c r="S62" s="0">
-        <v>0.21361567753320312</v>
+        <v>0.21361567753320313</v>
       </c>
       <c r="T62" s="0">
         <v>0.24585125998770721</v>
@@ -22457,7 +22458,7 @@
         <v>0.046352627614577861</v>
       </c>
       <c r="BN62" s="0">
-        <v>0.031046258925799416</v>
+        <v>0.031046258925799417</v>
       </c>
       <c r="BO62" s="0">
         <v>0.1913767871214678</v>
@@ -22496,13 +22497,13 @@
         <v>0.013164823591363863</v>
       </c>
       <c r="CA62" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB62" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC62" s="0">
-        <v>0.024996875390576156</v>
+        <v>0.024996875390576157</v>
       </c>
       <c r="CD62" s="0">
         <v>0.01282051282051281</v>
@@ -22642,7 +22643,7 @@
         <v>0.15494533872772764</v>
       </c>
       <c r="G63" s="0">
-        <v>0.093482905982906594</v>
+        <v>0.093482905982906595</v>
       </c>
       <c r="H63" s="0">
         <v>0.20183671409829579</v>
@@ -22657,13 +22658,13 @@
         <v>0.15203344735841984</v>
       </c>
       <c r="L63" s="0">
-        <v>0.19534718522465055</v>
+        <v>0.19534718522465056</v>
       </c>
       <c r="M63" s="0">
         <v>0.20790020790020927</v>
       </c>
       <c r="N63" s="0">
-        <v>0.15576323987539042</v>
+        <v>0.15576323987539043</v>
       </c>
       <c r="O63" s="0">
         <v>0.19115417573001248</v>
@@ -22825,7 +22826,7 @@
         <v>0.25892153551728192</v>
       </c>
       <c r="BP63" s="0">
-        <v>0.13962375073486274</v>
+        <v>0.13962375073486275</v>
       </c>
       <c r="BQ63" s="0">
         <v>0</v>
@@ -22888,7 +22889,7 @@
         <v>0.031625553447185532</v>
       </c>
       <c r="CK63" s="0">
-        <v>0.0056761742585497744</v>
+        <v>0.0056761742585497745</v>
       </c>
       <c r="CL63" s="0">
         <v>0.012631047113805817</v>
@@ -22989,7 +22990,7 @@
         <v>0.19321338002656668</v>
       </c>
       <c r="B64" s="0">
-        <v>0.17561465127947803</v>
+        <v>0.17561465127947804</v>
       </c>
       <c r="C64" s="0">
         <v>0.22389158933568987</v>
@@ -23127,7 +23128,7 @@
         <v>0</v>
       </c>
       <c r="AV64" s="0">
-        <v>0.0074521201281764603</v>
+        <v>0.0074521201281764604</v>
       </c>
       <c r="AW64" s="0">
         <v>0</v>
@@ -23223,7 +23224,7 @@
         <v>0.050125313283207976</v>
       </c>
       <c r="CB64" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC64" s="0">
         <v>0.037495313085864235</v>
@@ -23390,7 +23391,7 @@
         <v>0.10384215991692618</v>
       </c>
       <c r="O65" s="0">
-        <v>0.098872849515522956</v>
+        <v>0.098872849515522957</v>
       </c>
       <c r="P65" s="0">
         <v>0.19336859466530154</v>
@@ -23489,7 +23490,7 @@
         <v>0.0061819980217606282</v>
       </c>
       <c r="AV65" s="0">
-        <v>0.0074521201281764603</v>
+        <v>0.0074521201281764604</v>
       </c>
       <c r="AW65" s="0">
         <v>0</v>
@@ -23821,7 +23822,7 @@
         <v>0.052002080083203284</v>
       </c>
       <c r="AL66" s="0">
-        <v>0.051589604694653977</v>
+        <v>0.051589604694653978</v>
       </c>
       <c r="AM66" s="0">
         <v>0</v>
@@ -23851,7 +23852,7 @@
         <v>0</v>
       </c>
       <c r="AV66" s="0">
-        <v>0.0074521201281764603</v>
+        <v>0.0074521201281764604</v>
       </c>
       <c r="AW66" s="0">
         <v>0</v>
@@ -23947,7 +23948,7 @@
         <v>0.050125313283207976</v>
       </c>
       <c r="CB66" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC66" s="0">
         <v>0</v>
@@ -24159,7 +24160,7 @@
         <v>0.023640661938534435</v>
       </c>
       <c r="AD67" s="0">
-        <v>0.023792529145848357</v>
+        <v>0.023792529145848358</v>
       </c>
       <c r="AE67" s="0">
         <v>0</v>
@@ -24234,7 +24235,7 @@
         <v>0.078848807411788416</v>
       </c>
       <c r="BC67" s="0">
-        <v>0.033858134416793854</v>
+        <v>0.033858134416793855</v>
       </c>
       <c r="BD67" s="0">
         <v>0</v>
@@ -24282,7 +24283,7 @@
         <v>0</v>
       </c>
       <c r="BS67" s="0">
-        <v>0.0040389353366452867</v>
+        <v>0.0040389353366452868</v>
       </c>
       <c r="BT67" s="0">
         <v>0.11023488510133202</v>
@@ -24476,7 +24477,7 @@
         <v>0.093457943925232864</v>
       </c>
       <c r="O68" s="0">
-        <v>0.046140663107243698</v>
+        <v>0.046140663107243699</v>
       </c>
       <c r="P68" s="0">
         <v>0.06824773929363534</v>
@@ -24695,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="CJ68" s="0">
-        <v>0.031625553447185067</v>
+        <v>0.031625553447185068</v>
       </c>
       <c r="CK68" s="0">
         <v>0</v>
@@ -24820,7 +24821,7 @@
         <v>0.07064284993440352</v>
       </c>
       <c r="I69" s="0">
-        <v>0.038759689922480869</v>
+        <v>0.03875968992248087</v>
       </c>
       <c r="J69" s="0">
         <v>0.02557708293369158</v>
@@ -25314,7 +25315,7 @@
         <v>0.018525379770285136</v>
       </c>
       <c r="BA70" s="0">
-        <v>0.094369298521546865</v>
+        <v>0.094369298521546866</v>
       </c>
       <c r="BB70" s="0">
         <v>0.04928050463236703</v>
@@ -25628,7 +25629,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="0">
-        <v>0.02228660574994443</v>
+        <v>0.022286605749944431</v>
       </c>
       <c r="AL71" s="0">
         <v>0</v>
@@ -25730,7 +25731,7 @@
         <v>0</v>
       </c>
       <c r="BS71" s="0">
-        <v>0.0040389353366452867</v>
+        <v>0.0040389353366452868</v>
       </c>
       <c r="BT71" s="0">
         <v>0.038158229458153392</v>
@@ -25903,7 +25904,7 @@
         <v>0.013354700854700743</v>
       </c>
       <c r="H72" s="0">
-        <v>0.020183671409829278</v>
+        <v>0.020183671409829279</v>
       </c>
       <c r="I72" s="0">
         <v>0.027685492801771641</v>
@@ -26065,7 +26066,7 @@
         <v>0.0035861574323112488</v>
       </c>
       <c r="BJ72" s="0">
-        <v>0.018426386585590412</v>
+        <v>0.018426386585590413</v>
       </c>
       <c r="BK72" s="0">
         <v>0</v>
@@ -26612,7 +26613,7 @@
         <v>0.016725204883759687</v>
       </c>
       <c r="C74" s="0">
-        <v>0.0088378258948297993</v>
+        <v>0.0088378258948297994</v>
       </c>
       <c r="D74" s="0">
         <v>0.0027320165013796456</v>
@@ -26627,7 +26628,7 @@
         <v>0</v>
       </c>
       <c r="H74" s="0">
-        <v>0.020183671409829278</v>
+        <v>0.020183671409829279</v>
       </c>
       <c r="I74" s="0">
         <v>0.011074197120708658</v>
@@ -27013,7 +27014,7 @@
         <v>0</v>
       </c>
       <c r="P75" s="0">
-        <v>0.0056873116078030288</v>
+        <v>0.0056873116078030289</v>
       </c>
       <c r="Q75" s="0">
         <v>0</v>
@@ -27707,7 +27708,7 @@
         <v>0.0031149736784723912</v>
       </c>
       <c r="F77" s="0">
-        <v>0.0086080743737625177</v>
+        <v>0.0086080743737625178</v>
       </c>
       <c r="G77" s="0">
         <v>0</v>
@@ -28823,7 +28824,7 @@
         <v>0</v>
       </c>
       <c r="P80" s="0">
-        <v>0.0056873116078030288</v>
+        <v>0.0056873116078030289</v>
       </c>
       <c r="Q80" s="0">
         <v>0</v>
